--- a/surname_tracker/student_scores.xlsx
+++ b/surname_tracker/student_scores.xlsx
@@ -436,11 +436,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Arglen</t>
+          <t>arglen</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
